--- a/etf_holdings/2026-10-14_common_holdings_all.xlsx
+++ b/etf_holdings/2026-10-14_common_holdings_all.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.79%</t>
+          <t>10.73%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -662,7 +662,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14.03%</t>
+          <t>13.95%</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -675,7 +675,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9.43%</t>
+          <t>9.58%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.72%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -701,7 +701,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>13.81%</t>
+          <t>13.75%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -714,11 +714,11 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>14.02%</t>
+          <t>14.81%</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>1112000</v>
+        <v>1416000</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -727,11 +727,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>6.22%</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1116000</v>
+        <v>1166000</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="AA2" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.28%</t>
+          <t>9.25%</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -779,11 +779,11 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>8.35%</t>
+          <t>8.26%</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>341000</v>
+        <v>333000</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>8.85%</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -800,12 +800,12 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>107.07%</t>
+          <t>107.74%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>8.92%</t>
+          <t>8.98%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>8.45%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -848,7 +848,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10.04%</t>
+          <t>9.94%</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.03%</t>
+          <t>4.70%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>5.54%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -900,11 +900,11 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>95000</v>
+        <v>152000</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6.32%</t>
+          <t>5.64%</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="AA3" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.87%</t>
         </is>
       </c>
       <c r="AD3" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>6.23%</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>106000</v>
+        <v>113000</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -986,12 +986,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>65.73%</t>
+          <t>64.50%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>5.48%</t>
+          <t>5.38%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.18%</t>
+          <t>8.05%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6.59%</t>
+          <t>6.69%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>6.35%</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="AA4" t="n">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>5.47%</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>34000</v>
+        <v>33000</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>6.15%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>56.85%</t>
+          <t>56.67%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.17%</t>
+          <t>7.21%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.53%</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>126000</v>
+        <v>145000</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1285,11 +1285,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>6.55%</t>
+          <t>6.47%</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>894000</v>
+        <v>921000</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="AA5" t="n">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>51.03%</t>
+          <t>50.98%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
